--- a/Excel/8. Excel_IF_IFs/CountIf_if_Numerical.xlsx
+++ b/Excel/8. Excel_IF_IFs/CountIf_if_Numerical.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Weekend\Excel\8. Excel_IF_IFs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0602C85F-4F81-4EC9-A030-953AA57DA11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C30AE1F-B69C-4228-A3DB-E92B1180BBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="43">
   <si>
     <t>First Name</t>
   </si>
@@ -151,6 +151,21 @@
   </si>
   <si>
     <t>Nested If</t>
+  </si>
+  <si>
+    <t>countif for HR</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Number of Males</t>
+  </si>
+  <si>
+    <t>Number of female</t>
   </si>
 </sst>
 </file>
@@ -484,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultColWidth="17.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="19.6640625" customWidth="1"/>
@@ -675,6 +690,9 @@
         <f t="shared" si="2"/>
         <v>220-Yes</v>
       </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
       <c r="K5">
         <f t="shared" si="3"/>
         <v>1</v>
@@ -712,6 +730,10 @@
         <f t="shared" si="2"/>
         <v>170-No</v>
       </c>
+      <c r="I6">
+        <f>COUNTIF(C2:C11,"HR")</f>
+        <v>3</v>
+      </c>
       <c r="K6">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -786,6 +808,10 @@
         <f t="shared" si="2"/>
         <v>230-Yes</v>
       </c>
+      <c r="I8">
+        <f>COUNTIF(C2:C11,"IT")</f>
+        <v>4</v>
+      </c>
       <c r="K8">
         <f t="shared" si="3"/>
         <v>1</v>
@@ -911,14 +937,138 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="F21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22">
+        <f>IF(D22="Male",0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <f>COUNTIF(E22:E33,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G22">
+        <f>COUNTIF(E22:E33,1)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23">
+        <f t="shared" ref="E23:E33" si="5">IF(D23="Male",0,1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D26" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D29" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D33" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
